--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0045.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0045.xlsx
@@ -968,7 +968,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Giữa giới thương nhân, có một &lt;color=yellow&gt;"code"&lt;/color&gt; bí ẩn trong cách pha chế đồ uống.</t>
+          <t>Giữa giới thương nhân, có một &lt;color=yellow&gt;"mật mã"&lt;/color&gt; bí ẩn trong cách pha chế đồ uống.</t>
         </is>
       </c>
     </row>
@@ -1750,7 +1750,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Hello.</t>
+          <t>Xin chào.</t>
         </is>
       </c>
     </row>
@@ -2595,7 +2595,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Cậu... Tại sao lại ở đây?!</t>
+          <t>Mày... Tại sao lại ở đây?!</t>
         </is>
       </c>
     </row>
@@ -6430,7 +6430,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Phù, nợ cậu một mạng đấy! Mất mấy trang này thì Hội sẽ không tha cho ta đâu.</t>
+          <t>Phù, nợ cậu một mạng đấy! Mất mấy trang này thì Hội sẽ không tha cho tao đâu.</t>
         </is>
       </c>
     </row>
@@ -9810,7 +9810,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Cậu phải tập luyện trước khi gia nhập Hiệp Hội Tiên Phong à?</t>
+          <t>Mày phải tập luyện trước khi gia nhập Hiệp Hội Tiên Phong à?</t>
         </is>
       </c>
     </row>
@@ -13450,7 +13450,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Ta đã mơ thấy đủ mọi tình huống có thể xảy ra sau khi gia nhập Hiệp Hội Tiên Phong rồi.</t>
+          <t>Tao đã mơ thấy đủ mọi tình huống có thể xảy ra sau khi gia nhập Hiệp Hội Tiên Phong rồi.</t>
         </is>
       </c>
     </row>
@@ -14685,7 +14685,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Haha, ta hiểu ý ngươi rồi—chưa bao giờ dốc hết sức đánh ta phải không? Thế thì không được đâu!</t>
+          <t>Haha, tao hiểu ý mày rồi—chưa bao giờ dốc hết sức đánh tao phải không? Thế thì không được đâu!</t>
         </is>
       </c>
     </row>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Đúng rồi! Thằng em trai Fratellino của ta—nó bảo ra ngoài lấy mấy tài liệu gì đó. Không biết giờ nó có chăm sóc bản thân tốt không nữa.</t>
+          <t>Đúng rồi! Thằng em trai Fratellino của tao—nó bảo ra ngoài lấy mấy tài liệu gì đó. Không biết giờ nó có chăm sóc bản thân tốt không nữa.</t>
         </is>
       </c>
     </row>
@@ -15920,7 +15920,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Thật lòng, là lỗi của ta. Nếu lúc đó ta mạnh hơn... Thôi, nói nhiều làm gì, đi nào!</t>
+          <t>Thật lòng, là lỗi của tao. Nếu lúc đó tao mạnh hơn... Thôi, nói nhiều làm gì, đi nào!</t>
         </is>
       </c>
     </row>
@@ -16245,7 +16245,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Khi nghe Fratellino nói muốn gia nhập Hiệp Hội Tiên Phong, ta lập tức nghĩ: "À, đây là bước đầu tiên của ta rồi!"</t>
+          <t>Khi nghe Fratellino nói muốn gia nhập Hiệp Hội Tiên Phong, tao lập tức nghĩ: "À, đây là bước đầu tiên của tao rồi!"</t>
         </is>
       </c>
     </row>
@@ -17350,7 +17350,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Haha, ta sắp về Egla Town một thời gian. Có khi mình gặp nhau ở đó! Ta vẫn còn nợ cậu một lời cảm ơn to đấy!</t>
+          <t>Haha, tao sắp về Egla Town một thời gian. Có khi mình gặp nhau ở đó! Tao vẫn còn nợ cậu một lời cảm ơn to đấy!</t>
         </is>
       </c>
     </row>
@@ -18000,7 +18000,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Buông ta ra! Ồ, hóa ra là cậu, ân nhân của ta à.</t>
+          <t>Buông tao ra! Ồ, hóa ra là cậu, ân nhân của tao à.</t>
         </is>
       </c>
     </row>
@@ -19170,7 +19170,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Cậu phải tập luyện trước khi gia nhập Hiệp Hội Tiên Phong à?</t>
+          <t>Mày phải tập luyện trước khi gia nhập Hiệp Hội Tiên Phong à?</t>
         </is>
       </c>
     </row>
@@ -19885,7 +19885,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Ta sẽ không nói vậy đâu.</t>
+          <t>Tao sẽ không nói vậy đâu.</t>
         </is>
       </c>
     </row>
